--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484844_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484844_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8262</v>
+        <v>3.691</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6394</v>
+        <v>4.4776</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8131</v>
+        <v>-0.7867</v>
       </c>
       <c r="G2" t="n">
         <v>2.9907</v>
@@ -610,13 +610,13 @@
         <v>1.887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9382</v>
+        <v>-0.0735</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0582</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.1464</v>
       </c>
       <c r="V2" t="n">
         <v>0.019</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. MARCO CLIMENT</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8245</v>
+        <v>2.8017</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4134</v>
+        <v>2.8017</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4111</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0294</v>
+        <v>2.8017</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2285</v>
+        <v>0.9509</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1991</v>
+        <v>1.8509</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4361</v>
+        <v>2.8017</v>
       </c>
       <c r="K3" t="n">
-        <v>2.246</v>
+        <v>0.9509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1901</v>
+        <v>1.8509</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4067</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0175</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3892</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5308</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1851</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3458</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>F. MARCO CLIMENT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8017</v>
+        <v>2.3323</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8017</v>
+        <v>2.2386</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8017</v>
+        <v>0.0294</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9509</v>
+        <v>0.2285</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8509</v>
+        <v>-0.1991</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8017</v>
+        <v>2.4361</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9509</v>
+        <v>2.246</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8509</v>
+        <v>0.1901</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-2.4067</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-2.0175</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.3892</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0386</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.0103</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0429</v>
+        <v>1.5683</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4937</v>
+        <v>4.1344</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5492</v>
+        <v>-2.5661</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5468</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3561</v>
+        <v>-0.0767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9029</v>
+        <v>0.9049</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2556</v>
+        <v>3.9815</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1323</v>
+        <v>2.5575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1234</v>
+        <v>1.424</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2911</v>
+        <v>-3.1533</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4883</v>
+        <v>-2.6342</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7795</v>
+        <v>-0.5191</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5526</v>
+        <v>-0.0147</v>
       </c>
       <c r="T5" t="n">
-        <v>0.238</v>
+        <v>0.0399</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3146</v>
+        <v>-0.0546</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.5306</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2894</v>
+        <v>0.2988</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3354</v>
+        <v>1.2317</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0332</v>
+        <v>0.5468</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3475</v>
+        <v>-0.3561</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3807</v>
+        <v>0.9029</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5132</v>
+        <v>0.2556</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2664</v>
+        <v>0.1323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2468</v>
+        <v>0.1234</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5464</v>
+        <v>0.2911</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9189</v>
+        <v>-0.4883</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.7795</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2704</v>
+        <v>0.0403</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0029</v>
+        <v>0.0432</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2675</v>
+        <v>-0.0029</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.038</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8816000000000001</v>
+        <v>1.1632</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6859</v>
+        <v>2.4456</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8042</v>
+        <v>-1.2824</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8280999999999999</v>
+        <v>-0.0332</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0767</v>
+        <v>0.3475</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9049</v>
+        <v>-0.3807</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9815</v>
+        <v>2.5132</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5575</v>
+        <v>2.2664</v>
       </c>
       <c r="L7" t="n">
-        <v>1.424</v>
+        <v>0.2468</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1533</v>
+        <v>-2.5464</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.6342</v>
+        <v>-1.9189</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5191</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P7" t="n">
         <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7013</v>
+        <v>0.4796</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4086</v>
+        <v>0.1591</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2927</v>
+        <v>0.3204</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.038</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>-0.038</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4378</v>
+        <v>0.6926</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6407</v>
+        <v>0.1357</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2029</v>
+        <v>0.5569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9345</v>
+        <v>-0.9423</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1121</v>
+        <v>0.2966</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1776</v>
+        <v>-1.239</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8062</v>
+        <v>-0.9192</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3735</v>
+        <v>0.4281</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5673</v>
+        <v>-1.3473</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1284</v>
+        <v>-0.0231</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2614</v>
+        <v>-0.1315</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3897</v>
+        <v>0.1083</v>
       </c>
       <c r="P8" t="n">
         <v>0.9435</v>
@@ -1078,28 +1078,28 @@
         <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1258</v>
+        <v>-0.5538</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4761</v>
+        <v>-0.4921</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3503</v>
+        <v>-0.0617</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.566</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.547</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9244</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1383</v>
+        <v>-0.0616</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3128</v>
+        <v>0.1149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4511</v>
+        <v>-0.1764</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9423</v>
+        <v>0.9345</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2966</v>
+        <v>1.1121</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.239</v>
+        <v>-0.1776</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9192</v>
+        <v>0.8062</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4281</v>
+        <v>1.3735</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3473</v>
+        <v>-0.5673</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0231</v>
+        <v>0.1284</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1315</v>
+        <v>-0.2614</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1083</v>
+        <v>0.3897</v>
       </c>
       <c r="P9" t="n">
         <v>0.9435</v>
@@ -1156,22 +1156,22 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1081</v>
+        <v>-0.3736</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9406</v>
+        <v>-0.0497</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1675</v>
+        <v>-0.3239</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>-1.566</v>
       </c>
       <c r="W9" t="n">
-        <v>1.547</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5706</v>
+        <v>-0.5685</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5021</v>
+        <v>0.4248</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0727</v>
+        <v>-0.9933</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1678</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4085</v>
+        <v>0.4106</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0058</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4027</v>
+        <v>0.4821</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6226</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1675</v>
+        <v>-1.9281</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5798</v>
+        <v>0.8721</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7473</v>
+        <v>-2.8002</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0068</v>
@@ -1312,13 +1312,13 @@
         <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6137</v>
+        <v>-0.3743</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4115</v>
+        <v>-0.1192</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2022</v>
+        <v>-0.2551</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9244</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4062</v>
+        <v>-2.8707</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7851</v>
+        <v>-2.4083</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6212</v>
+        <v>-0.4624</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4098</v>
@@ -1390,13 +1390,13 @@
         <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0035</v>
+        <v>-0.461</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6554</v>
+        <v>0.0321</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6519</v>
+        <v>-0.4932</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9434</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.762799999999999</v>
+        <v>8.3508</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9482</v>
+        <v>15.5359</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.1854</v>
+        <v>-7.185199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>3.571299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>14.1525</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4697</v>
+        <v>-0.8817999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2556</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2140000000000001</v>
+        <v>-0.2142</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8868</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0245</v>
+        <v>2.3985</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1585</v>
+        <v>3.5995</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.134</v>
+        <v>-1.201</v>
       </c>
       <c r="G14" t="n">
         <v>2.6682</v>
@@ -1546,13 +1546,13 @@
         <v>0.9435</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2431</v>
+        <v>1.6172</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2731</v>
+        <v>0.7141</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>0.9031</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9434</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0528</v>
+        <v>2.2909</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0889</v>
+        <v>4.7735</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.036</v>
+        <v>-2.4826</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0914</v>
+        <v>-0.9971</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3249</v>
+        <v>-0.1941</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7664</v>
+        <v>-0.803</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6498</v>
+        <v>2.4106</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9917</v>
+        <v>2.2617</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6581</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5584</v>
+        <v>-3.4077</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-2.4558</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1083</v>
+        <v>-0.952</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5661</v>
+        <v>0.1887</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>1.452</v>
+        <v>-0.3155</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3826</v>
+        <v>-0.4103</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0694</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9244</v>
+        <v>3.4148</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9244</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4501</v>
+        <v>1.3263</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0914</v>
+        <v>2.3094</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6414</v>
+        <v>-0.9831</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9971</v>
+        <v>2.0914</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1941</v>
+        <v>1.3249</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.803</v>
+        <v>0.7664</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4106</v>
+        <v>2.6498</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2617</v>
+        <v>1.9917</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1489</v>
+        <v>0.6581</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4077</v>
+        <v>-0.5584</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.4558</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.952</v>
+        <v>0.1083</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1887</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1563</v>
+        <v>0.7254</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0923</v>
+        <v>0.6031</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.064</v>
+        <v>0.1223</v>
       </c>
       <c r="V17" t="n">
-        <v>3.4148</v>
+        <v>-0.9244</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3018</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1932</v>
+        <v>0.9449</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2266</v>
+        <v>0.2605</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4198</v>
+        <v>0.6844</v>
       </c>
       <c r="G18" t="n">
         <v>1.3479</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.532</v>
+        <v>0.2197</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3527</v>
+        <v>0.1344</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1793</v>
+        <v>0.0853</v>
       </c>
       <c r="V18" t="n">
         <v>0.3208</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2946</v>
+        <v>-1.4101</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8262</v>
+        <v>-1.0211</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4683</v>
+        <v>-0.389</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1227</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1117</v>
+        <v>-0.0038</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0646</v>
+        <v>-0.1303</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0471</v>
+        <v>0.1265</v>
       </c>
       <c r="V19" t="n">
         <v>3.7356</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.726</v>
+        <v>-1.4783</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0919</v>
+        <v>0.2867</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8179</v>
+        <v>-1.765</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5262</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3886</v>
+        <v>-0.1408</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2939</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2274</v>
+        <v>-2.0061</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2923</v>
+        <v>-1.0975</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9351</v>
+        <v>-0.9086</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1716</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4897</v>
+        <v>-0.2684</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4703</v>
+        <v>-0.2754</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0194</v>
+        <v>0.0071</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7324</v>
+        <v>-2.3427</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0805</v>
+        <v>-2.6907</v>
       </c>
       <c r="F22" t="n">
         <v>0.3481</v>
@@ -2170,10 +2170,10 @@
         <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2257</v>
+        <v>0.164</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2939</v>
+        <v>0.0958</v>
       </c>
       <c r="U22" t="n">
         <v>0.0682</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0522</v>
+        <v>-4.0315</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5289</v>
+        <v>-3.0483</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.5811</v>
+        <v>-0.9831</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0213</v>
+        <v>-1.6184</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0305</v>
+        <v>-2.1381</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0518</v>
+        <v>0.5196</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3831</v>
+        <v>-0.4962</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2016</v>
+        <v>-0.4962</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1816</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.4044</v>
+        <v>-1.1222</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.171</v>
+        <v>-1.6419</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2334</v>
+        <v>0.5196</v>
       </c>
       <c r="P23" t="n">
+        <v>-2.4531</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.8305</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.3774</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-0.9435</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3209</v>
-      </c>
       <c r="S23" t="n">
-        <v>0.0065</v>
+        <v>0.3418</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0893</v>
+        <v>0.2783</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0828</v>
+        <v>0.0635</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.4148</v>
+        <v>-0.3018</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.4148</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0676</v>
+        <v>-4.0703</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2432</v>
+        <v>2.4315</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8244</v>
+        <v>-6.5018</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6184</v>
+        <v>-1.0213</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1381</v>
+        <v>0.0305</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5196</v>
+        <v>-1.0518</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4962</v>
+        <v>3.3831</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.4962</v>
+        <v>3.2016</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.1816</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1222</v>
+        <v>-4.4044</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6419</v>
+        <v>-3.171</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5196</v>
+        <v>-1.2334</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.4531</v>
+        <v>0.3774</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3057</v>
+        <v>-0.0116</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0835</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2222</v>
+        <v>-0.0034</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3018</v>
+        <v>-3.4148</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3018</v>
+        <v>-3.4148</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.811800000000002</v>
+        <v>-6.810599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>7.858600000000001</v>
+        <v>7.371300000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.6703</v>
+        <v>-14.1817</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.533899999999999</v>
+        <v>-2.5339</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2444</v>
+        <v>-1.244400000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-1.2895</v>
@@ -2404,13 +2404,13 @@
         <v>5.661</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3267</v>
+        <v>2.328</v>
       </c>
       <c r="T25" t="n">
-        <v>1.389999999999999</v>
+        <v>0.9024</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9368</v>
+        <v>1.4256</v>
       </c>
       <c r="V25" t="n">
         <v>1.8868</v>
